--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charlyboyapple/bellezagdl-backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8296370E-9286-9A46-AFB5-8DC71F97A88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B362C0F8-88B1-3C4A-8285-A6336D6287E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31220" yWindow="7140" windowWidth="27140" windowHeight="12560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36820" yWindow="10640" windowWidth="31240" windowHeight="13460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="43">
   <si>
     <t>Alby</t>
   </si>
@@ -147,6 +147,21 @@
   </si>
   <si>
     <t>Algodón Plisado 100gr Alby</t>
+  </si>
+  <si>
+    <t>01 Rojo</t>
+  </si>
+  <si>
+    <t>02 Blanco</t>
+  </si>
+  <si>
+    <t>A50G_01</t>
+  </si>
+  <si>
+    <t>A50G_02</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -508,18 +523,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="37.33203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29" style="2" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="37.33203125" style="2"/>
+    <col min="9" max="9" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="37.33203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -644,7 +661,7 @@
         <v>10</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -658,19 +675,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2">
-        <v>32</v>
+        <v>13.2</v>
       </c>
       <c r="H5" s="2">
         <v>10</v>
@@ -679,7 +696,7 @@
         <v>24</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.2">
@@ -690,19 +707,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G6" s="2">
-        <v>17.7</v>
+        <v>13.2</v>
       </c>
       <c r="H6" s="2">
         <v>10</v>
@@ -722,19 +739,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="2">
         <v>32</v>
-      </c>
-      <c r="G7" s="2">
-        <v>25</v>
       </c>
       <c r="H7" s="2">
         <v>10</v>
@@ -743,7 +760,7 @@
         <v>24</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" x14ac:dyDescent="0.2">
@@ -754,19 +771,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G8" s="2">
-        <v>21.3</v>
+        <v>17.7</v>
       </c>
       <c r="H8" s="2">
         <v>10</v>
@@ -775,6 +792,70 @@
         <v>24</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="2">
+        <v>25</v>
+      </c>
+      <c r="H9" s="2">
+        <v>10</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="2">
+        <v>21.3</v>
+      </c>
+      <c r="H10" s="2">
+        <v>10</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>34</v>
       </c>
     </row>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charlyboyapple/bellezagdl-backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE7E4DC-1332-9642-ACA2-C9158EFA672E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAA95BE-2A93-9C4C-9764-7BAA535FAA66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36460" yWindow="2600" windowWidth="31240" windowHeight="13460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15700" yWindow="4800" windowWidth="31240" windowHeight="13460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,721 +92,721 @@
     <t>nuevo</t>
   </si>
   <si>
+    <t>Adara</t>
+  </si>
+  <si>
+    <t>Rostro / Borlas</t>
+  </si>
+  <si>
+    <t>Borla Triangular Adara</t>
+  </si>
+  <si>
+    <t>PU003</t>
+  </si>
+  <si>
+    <t>Amor Us</t>
+  </si>
+  <si>
+    <t>Cejas / Brochas</t>
+  </si>
+  <si>
+    <t>Brocha 920 Amor Us</t>
+  </si>
+  <si>
+    <t>BA920</t>
+  </si>
+  <si>
+    <t>Brocha Premium 120 Amor Us</t>
+  </si>
+  <si>
+    <t>BA120</t>
+  </si>
+  <si>
+    <t>Ojos / Corrector</t>
+  </si>
+  <si>
+    <t>Corrector Liquido Studio Adara</t>
+  </si>
+  <si>
+    <t>LC002</t>
+  </si>
+  <si>
+    <t>Rostro / Correctores</t>
+  </si>
+  <si>
+    <t>Corrector Mate Amor Us</t>
+  </si>
+  <si>
+    <t>CO-BFF</t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>Cabello / Accesorios para Cabello</t>
+  </si>
+  <si>
+    <t>Dona Licra Mediana</t>
+  </si>
+  <si>
+    <t>72A</t>
+  </si>
+  <si>
+    <t>Rostro / Esponjas</t>
+  </si>
+  <si>
+    <t>Esponja para Difuminar Adara</t>
+  </si>
+  <si>
+    <t>SP006</t>
+  </si>
+  <si>
+    <t>Rostro / Primer y Fijadores</t>
+  </si>
+  <si>
+    <t>Fijador de Maquillaje Pepino Amor Us</t>
+  </si>
+  <si>
+    <t>CO-MLSPD</t>
+  </si>
+  <si>
+    <t>Cejas / Ceras</t>
+  </si>
+  <si>
+    <t>Gel Fijador de Ceja Amor Us</t>
+  </si>
+  <si>
+    <t>CO-SRBD</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>Cabello / Gorro</t>
+  </si>
+  <si>
+    <t>Gorro para  Dormir Satín Africa</t>
+  </si>
+  <si>
+    <t>GDSA</t>
+  </si>
+  <si>
+    <t>Pestañas / Pestañas Postizas</t>
+  </si>
+  <si>
+    <t>Kit Pestañas Diy Kit Ml Amor Us</t>
+  </si>
+  <si>
+    <t>DIY-KIT</t>
+  </si>
+  <si>
+    <t>Kit Pestañas Diy Kit Sl Amor Us</t>
+  </si>
+  <si>
+    <t>DIY-KITSM</t>
+  </si>
+  <si>
+    <t>Varios Accesorios / Varios Accesorios</t>
+  </si>
+  <si>
+    <t>Liga Licra Chica</t>
+  </si>
+  <si>
+    <t>61A</t>
+  </si>
+  <si>
+    <t>Liga Licra Grande</t>
+  </si>
+  <si>
+    <t>90A</t>
+  </si>
+  <si>
+    <t>Pestañas / Pegamentos</t>
+  </si>
+  <si>
+    <t>Pegamento Glue And Seal Diy Amor Us</t>
+  </si>
+  <si>
+    <t>CO-GNSD</t>
+  </si>
+  <si>
+    <t>Pestaña 3D Amor Us</t>
+  </si>
+  <si>
+    <t>3D-01</t>
+  </si>
+  <si>
+    <t>Pestaña Diy Extensions Ml Amor Us</t>
+  </si>
+  <si>
+    <t>DIY-ML</t>
+  </si>
+  <si>
+    <t>Pestaña Diy Extensions Sm Amor Us</t>
+  </si>
+  <si>
+    <t>DIY-SM</t>
+  </si>
+  <si>
+    <t>RSCA Rizador Sin Calor Africa</t>
+  </si>
+  <si>
+    <t>RSCA</t>
+  </si>
+  <si>
+    <t>Pestañas / Rizadores</t>
+  </si>
+  <si>
+    <t>Rizador 02 Adara</t>
+  </si>
+  <si>
+    <t>EC02</t>
+  </si>
+  <si>
+    <t>Cejas / Sombras</t>
+  </si>
+  <si>
+    <t>Sombra para Ceja Adara</t>
+  </si>
+  <si>
+    <t>EB001</t>
+  </si>
+  <si>
+    <t>01 Porcelain</t>
+  </si>
+  <si>
+    <t>02 Nude</t>
+  </si>
+  <si>
+    <t>03 Light Fawn</t>
+  </si>
+  <si>
+    <t>05 Petite Peach</t>
+  </si>
+  <si>
+    <t>06 Soft Yellow</t>
+  </si>
+  <si>
+    <t>07 Mint Green</t>
+  </si>
+  <si>
+    <t>08 Lilac Dream</t>
+  </si>
+  <si>
+    <t>01 Fair</t>
+  </si>
+  <si>
+    <t>02 Light</t>
+  </si>
+  <si>
+    <t>03 Medium Light</t>
+  </si>
+  <si>
+    <t>04 Medium Olive</t>
+  </si>
+  <si>
+    <t>05 Honey</t>
+  </si>
+  <si>
+    <t>06 Cacao</t>
+  </si>
+  <si>
+    <t>Dorado</t>
+  </si>
+  <si>
+    <t>Negro</t>
+  </si>
+  <si>
+    <t>Rosa</t>
+  </si>
+  <si>
+    <t>P-02</t>
+  </si>
+  <si>
+    <t>P-04</t>
+  </si>
+  <si>
+    <t>P-08</t>
+  </si>
+  <si>
+    <t>P-10</t>
+  </si>
+  <si>
+    <t>P-12</t>
+  </si>
+  <si>
+    <t>P-13</t>
+  </si>
+  <si>
+    <t>#01</t>
+  </si>
+  <si>
+    <t>#02</t>
+  </si>
+  <si>
+    <t>#03</t>
+  </si>
+  <si>
+    <t>#04</t>
+  </si>
+  <si>
+    <t>#05</t>
+  </si>
+  <si>
+    <t>#06</t>
+  </si>
+  <si>
+    <t>#07</t>
+  </si>
+  <si>
+    <t>#08</t>
+  </si>
+  <si>
+    <t>#09</t>
+  </si>
+  <si>
+    <t>#10</t>
+  </si>
+  <si>
+    <t>#11</t>
+  </si>
+  <si>
+    <t>#12</t>
+  </si>
+  <si>
+    <t>#13</t>
+  </si>
+  <si>
+    <t>#14</t>
+  </si>
+  <si>
+    <t>#15</t>
+  </si>
+  <si>
+    <t>#16</t>
+  </si>
+  <si>
+    <t>#17</t>
+  </si>
+  <si>
+    <t>#18</t>
+  </si>
+  <si>
+    <t>#19</t>
+  </si>
+  <si>
+    <t>#20</t>
+  </si>
+  <si>
+    <t>#21</t>
+  </si>
+  <si>
+    <t>#22</t>
+  </si>
+  <si>
+    <t>#23</t>
+  </si>
+  <si>
+    <t>#24</t>
+  </si>
+  <si>
+    <t>#25</t>
+  </si>
+  <si>
+    <t>#26</t>
+  </si>
+  <si>
+    <t>#27</t>
+  </si>
+  <si>
+    <t>#28</t>
+  </si>
+  <si>
+    <t>#29</t>
+  </si>
+  <si>
+    <t>#30</t>
+  </si>
+  <si>
+    <t>#31</t>
+  </si>
+  <si>
+    <t>#32</t>
+  </si>
+  <si>
+    <t>#33</t>
+  </si>
+  <si>
+    <t>#34</t>
+  </si>
+  <si>
+    <t>#35</t>
+  </si>
+  <si>
+    <t>#36</t>
+  </si>
+  <si>
+    <t>#37</t>
+  </si>
+  <si>
+    <t>#38</t>
+  </si>
+  <si>
+    <t>#39</t>
+  </si>
+  <si>
+    <t>#40</t>
+  </si>
+  <si>
+    <t>#41</t>
+  </si>
+  <si>
+    <t>#42</t>
+  </si>
+  <si>
+    <t>#43</t>
+  </si>
+  <si>
+    <t>#44</t>
+  </si>
+  <si>
+    <t>#45</t>
+  </si>
+  <si>
+    <t>#46</t>
+  </si>
+  <si>
+    <t>#47</t>
+  </si>
+  <si>
+    <t>#48</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>LC002_01</t>
+  </si>
+  <si>
+    <t>LC002_02</t>
+  </si>
+  <si>
+    <t>LC002_03</t>
+  </si>
+  <si>
+    <t>LC002_05</t>
+  </si>
+  <si>
+    <t>LC002_06</t>
+  </si>
+  <si>
+    <t>LC002_07</t>
+  </si>
+  <si>
+    <t>LC002_08</t>
+  </si>
+  <si>
+    <t>CO-BFF_01</t>
+  </si>
+  <si>
+    <t>CO-BFF_02</t>
+  </si>
+  <si>
+    <t>CO-BFF_03</t>
+  </si>
+  <si>
+    <t>CO-BFF_04</t>
+  </si>
+  <si>
+    <t>CO-BFF_05</t>
+  </si>
+  <si>
+    <t>CO-BFF_06</t>
+  </si>
+  <si>
+    <t>GDSA_DORADO</t>
+  </si>
+  <si>
+    <t>GDSA_NEGRO</t>
+  </si>
+  <si>
+    <t>GDSA_ROSA</t>
+  </si>
+  <si>
+    <t>DIY-KIT_02</t>
+  </si>
+  <si>
+    <t>DIY-KIT_04</t>
+  </si>
+  <si>
+    <t>DIY-KIT_08</t>
+  </si>
+  <si>
+    <t>DIY-KIT_10</t>
+  </si>
+  <si>
+    <t>DIY-KIT_12</t>
+  </si>
+  <si>
+    <t>DIY-KIT_13</t>
+  </si>
+  <si>
+    <t>DIY-KITSM_02</t>
+  </si>
+  <si>
+    <t>DIY-KITSM_04</t>
+  </si>
+  <si>
+    <t>DIY-KITSM_08</t>
+  </si>
+  <si>
+    <t>DIY-KITSM_10</t>
+  </si>
+  <si>
+    <t>DIY-KITSM_12</t>
+  </si>
+  <si>
+    <t>DIY-KITSM_133</t>
+  </si>
+  <si>
+    <t>3D-01_01</t>
+  </si>
+  <si>
+    <t>3D-01_02</t>
+  </si>
+  <si>
+    <t>3D-01_03</t>
+  </si>
+  <si>
+    <t>3D-01_04</t>
+  </si>
+  <si>
+    <t>3D-01_05</t>
+  </si>
+  <si>
+    <t>3D-01_06</t>
+  </si>
+  <si>
+    <t>3D-01_07</t>
+  </si>
+  <si>
+    <t>3D-01_08</t>
+  </si>
+  <si>
+    <t>3D-01_09</t>
+  </si>
+  <si>
+    <t>3D-01_10</t>
+  </si>
+  <si>
+    <t>3D-01_11</t>
+  </si>
+  <si>
+    <t>3D-01_12</t>
+  </si>
+  <si>
+    <t>3D-01_13</t>
+  </si>
+  <si>
+    <t>3D-01_14</t>
+  </si>
+  <si>
+    <t>3D-01_15</t>
+  </si>
+  <si>
+    <t>3D-01_16</t>
+  </si>
+  <si>
+    <t>3D-01_17</t>
+  </si>
+  <si>
+    <t>3D-01_18</t>
+  </si>
+  <si>
+    <t>3D-01_19</t>
+  </si>
+  <si>
+    <t>3D-01_20</t>
+  </si>
+  <si>
+    <t>3D-01_21</t>
+  </si>
+  <si>
+    <t>3D-01_22</t>
+  </si>
+  <si>
+    <t>3D-01_23</t>
+  </si>
+  <si>
+    <t>3D-01_24</t>
+  </si>
+  <si>
+    <t>3D-01_25</t>
+  </si>
+  <si>
+    <t>3D-01_26</t>
+  </si>
+  <si>
+    <t>3D-01_27</t>
+  </si>
+  <si>
+    <t>3D-01_28</t>
+  </si>
+  <si>
+    <t>3D-01_29</t>
+  </si>
+  <si>
+    <t>3D-01_30</t>
+  </si>
+  <si>
+    <t>3D-01_31</t>
+  </si>
+  <si>
+    <t>3D-01_32</t>
+  </si>
+  <si>
+    <t>3D-01_33</t>
+  </si>
+  <si>
+    <t>3D-01_34</t>
+  </si>
+  <si>
+    <t>3D-01_35</t>
+  </si>
+  <si>
+    <t>3D-01_36</t>
+  </si>
+  <si>
+    <t>3D-01_37</t>
+  </si>
+  <si>
+    <t>3D-01_38</t>
+  </si>
+  <si>
+    <t>3D-01_39</t>
+  </si>
+  <si>
+    <t>3D-01_40</t>
+  </si>
+  <si>
+    <t>3D-01_41</t>
+  </si>
+  <si>
+    <t>3D-01_42</t>
+  </si>
+  <si>
+    <t>3D-01_43</t>
+  </si>
+  <si>
+    <t>3D-01_44</t>
+  </si>
+  <si>
+    <t>3D-01_45</t>
+  </si>
+  <si>
+    <t>3D-01_46</t>
+  </si>
+  <si>
+    <t>3D-01_47</t>
+  </si>
+  <si>
+    <t>3D-01_48</t>
+  </si>
+  <si>
+    <t>DIY-ML_01</t>
+  </si>
+  <si>
+    <t>DIY-ML_02</t>
+  </si>
+  <si>
+    <t>DIY-ML_03</t>
+  </si>
+  <si>
+    <t>DIY-ML_04</t>
+  </si>
+  <si>
+    <t>DIY-ML_05</t>
+  </si>
+  <si>
+    <t>DIY-ML_06</t>
+  </si>
+  <si>
+    <t>DIY-ML_07</t>
+  </si>
+  <si>
+    <t>DIY-ML_08</t>
+  </si>
+  <si>
+    <t>DIY-ML_09</t>
+  </si>
+  <si>
+    <t>DIY-ML_10</t>
+  </si>
+  <si>
+    <t>DIY-ML_11</t>
+  </si>
+  <si>
+    <t>DIY-ML_12</t>
+  </si>
+  <si>
+    <t>DIY-ML_13</t>
+  </si>
+  <si>
+    <t>DIY-SM_01</t>
+  </si>
+  <si>
+    <t>DIY-SM_02</t>
+  </si>
+  <si>
+    <t>DIY-SM_03</t>
+  </si>
+  <si>
+    <t>DIY-SM_04</t>
+  </si>
+  <si>
+    <t>DIY-SM_05</t>
+  </si>
+  <si>
+    <t>DIY-SM_06</t>
+  </si>
+  <si>
+    <t>DIY-SM_07</t>
+  </si>
+  <si>
+    <t>DIY-SM_08</t>
+  </si>
+  <si>
+    <t>DIY-SM_09</t>
+  </si>
+  <si>
+    <t>DIY-SM_10</t>
+  </si>
+  <si>
+    <t>DIY-SM_11</t>
+  </si>
+  <si>
+    <t>DIY-SM_12</t>
+  </si>
+  <si>
+    <t>DIY-SM_13</t>
+  </si>
+  <si>
+    <t>EB001_01</t>
+  </si>
+  <si>
+    <t>EB001_02</t>
+  </si>
+  <si>
+    <t>EB001_03</t>
+  </si>
+  <si>
     <t>no</t>
-  </si>
-  <si>
-    <t>Adara</t>
-  </si>
-  <si>
-    <t>Rostro / Borlas</t>
-  </si>
-  <si>
-    <t>Borla Triangular Adara</t>
-  </si>
-  <si>
-    <t>PU003</t>
-  </si>
-  <si>
-    <t>Amor Us</t>
-  </si>
-  <si>
-    <t>Cejas / Brochas</t>
-  </si>
-  <si>
-    <t>Brocha 920 Amor Us</t>
-  </si>
-  <si>
-    <t>BA920</t>
-  </si>
-  <si>
-    <t>Brocha Premium 120 Amor Us</t>
-  </si>
-  <si>
-    <t>BA120</t>
-  </si>
-  <si>
-    <t>Ojos / Corrector</t>
-  </si>
-  <si>
-    <t>Corrector Liquido Studio Adara</t>
-  </si>
-  <si>
-    <t>LC002</t>
-  </si>
-  <si>
-    <t>Rostro / Correctores</t>
-  </si>
-  <si>
-    <t>Corrector Mate Amor Us</t>
-  </si>
-  <si>
-    <t>CO-BFF</t>
-  </si>
-  <si>
-    <t>Antonio</t>
-  </si>
-  <si>
-    <t>Cabello / Accesorios para Cabello</t>
-  </si>
-  <si>
-    <t>Dona Licra Mediana</t>
-  </si>
-  <si>
-    <t>72A</t>
-  </si>
-  <si>
-    <t>Rostro / Esponjas</t>
-  </si>
-  <si>
-    <t>Esponja para Difuminar Adara</t>
-  </si>
-  <si>
-    <t>SP006</t>
-  </si>
-  <si>
-    <t>Rostro / Primer y Fijadores</t>
-  </si>
-  <si>
-    <t>Fijador de Maquillaje Pepino Amor Us</t>
-  </si>
-  <si>
-    <t>CO-MLSPD</t>
-  </si>
-  <si>
-    <t>Cejas / Ceras</t>
-  </si>
-  <si>
-    <t>Gel Fijador de Ceja Amor Us</t>
-  </si>
-  <si>
-    <t>CO-SRBD</t>
-  </si>
-  <si>
-    <t>Africa</t>
-  </si>
-  <si>
-    <t>Cabello / Gorro</t>
-  </si>
-  <si>
-    <t>Gorro para  Dormir Satín Africa</t>
-  </si>
-  <si>
-    <t>GDSA</t>
-  </si>
-  <si>
-    <t>Pestañas / Pestañas Postizas</t>
-  </si>
-  <si>
-    <t>Kit Pestañas Diy Kit Ml Amor Us</t>
-  </si>
-  <si>
-    <t>DIY-KIT</t>
-  </si>
-  <si>
-    <t>Kit Pestañas Diy Kit Sl Amor Us</t>
-  </si>
-  <si>
-    <t>DIY-KITSM</t>
-  </si>
-  <si>
-    <t>Varios Accesorios / Varios Accesorios</t>
-  </si>
-  <si>
-    <t>Liga Licra Chica</t>
-  </si>
-  <si>
-    <t>61A</t>
-  </si>
-  <si>
-    <t>Liga Licra Grande</t>
-  </si>
-  <si>
-    <t>90A</t>
-  </si>
-  <si>
-    <t>Pestañas / Pegamentos</t>
-  </si>
-  <si>
-    <t>Pegamento Glue And Seal Diy Amor Us</t>
-  </si>
-  <si>
-    <t>CO-GNSD</t>
-  </si>
-  <si>
-    <t>Pestaña 3D Amor Us</t>
-  </si>
-  <si>
-    <t>3D-01</t>
-  </si>
-  <si>
-    <t>Pestaña Diy Extensions Ml Amor Us</t>
-  </si>
-  <si>
-    <t>DIY-ML</t>
-  </si>
-  <si>
-    <t>Pestaña Diy Extensions Sm Amor Us</t>
-  </si>
-  <si>
-    <t>DIY-SM</t>
-  </si>
-  <si>
-    <t>RSCA Rizador Sin Calor Africa</t>
-  </si>
-  <si>
-    <t>RSCA</t>
-  </si>
-  <si>
-    <t>Pestañas / Rizadores</t>
-  </si>
-  <si>
-    <t>Rizador 02 Adara</t>
-  </si>
-  <si>
-    <t>EC02</t>
-  </si>
-  <si>
-    <t>Cejas / Sombras</t>
-  </si>
-  <si>
-    <t>Sombra para Ceja Adara</t>
-  </si>
-  <si>
-    <t>EB001</t>
-  </si>
-  <si>
-    <t>01 Porcelain</t>
-  </si>
-  <si>
-    <t>02 Nude</t>
-  </si>
-  <si>
-    <t>03 Light Fawn</t>
-  </si>
-  <si>
-    <t>05 Petite Peach</t>
-  </si>
-  <si>
-    <t>06 Soft Yellow</t>
-  </si>
-  <si>
-    <t>07 Mint Green</t>
-  </si>
-  <si>
-    <t>08 Lilac Dream</t>
-  </si>
-  <si>
-    <t>01 Fair</t>
-  </si>
-  <si>
-    <t>02 Light</t>
-  </si>
-  <si>
-    <t>03 Medium Light</t>
-  </si>
-  <si>
-    <t>04 Medium Olive</t>
-  </si>
-  <si>
-    <t>05 Honey</t>
-  </si>
-  <si>
-    <t>06 Cacao</t>
-  </si>
-  <si>
-    <t>Dorado</t>
-  </si>
-  <si>
-    <t>Negro</t>
-  </si>
-  <si>
-    <t>Rosa</t>
-  </si>
-  <si>
-    <t>P-02</t>
-  </si>
-  <si>
-    <t>P-04</t>
-  </si>
-  <si>
-    <t>P-08</t>
-  </si>
-  <si>
-    <t>P-10</t>
-  </si>
-  <si>
-    <t>P-12</t>
-  </si>
-  <si>
-    <t>P-13</t>
-  </si>
-  <si>
-    <t>#01</t>
-  </si>
-  <si>
-    <t>#02</t>
-  </si>
-  <si>
-    <t>#03</t>
-  </si>
-  <si>
-    <t>#04</t>
-  </si>
-  <si>
-    <t>#05</t>
-  </si>
-  <si>
-    <t>#06</t>
-  </si>
-  <si>
-    <t>#07</t>
-  </si>
-  <si>
-    <t>#08</t>
-  </si>
-  <si>
-    <t>#09</t>
-  </si>
-  <si>
-    <t>#10</t>
-  </si>
-  <si>
-    <t>#11</t>
-  </si>
-  <si>
-    <t>#12</t>
-  </si>
-  <si>
-    <t>#13</t>
-  </si>
-  <si>
-    <t>#14</t>
-  </si>
-  <si>
-    <t>#15</t>
-  </si>
-  <si>
-    <t>#16</t>
-  </si>
-  <si>
-    <t>#17</t>
-  </si>
-  <si>
-    <t>#18</t>
-  </si>
-  <si>
-    <t>#19</t>
-  </si>
-  <si>
-    <t>#20</t>
-  </si>
-  <si>
-    <t>#21</t>
-  </si>
-  <si>
-    <t>#22</t>
-  </si>
-  <si>
-    <t>#23</t>
-  </si>
-  <si>
-    <t>#24</t>
-  </si>
-  <si>
-    <t>#25</t>
-  </si>
-  <si>
-    <t>#26</t>
-  </si>
-  <si>
-    <t>#27</t>
-  </si>
-  <si>
-    <t>#28</t>
-  </si>
-  <si>
-    <t>#29</t>
-  </si>
-  <si>
-    <t>#30</t>
-  </si>
-  <si>
-    <t>#31</t>
-  </si>
-  <si>
-    <t>#32</t>
-  </si>
-  <si>
-    <t>#33</t>
-  </si>
-  <si>
-    <t>#34</t>
-  </si>
-  <si>
-    <t>#35</t>
-  </si>
-  <si>
-    <t>#36</t>
-  </si>
-  <si>
-    <t>#37</t>
-  </si>
-  <si>
-    <t>#38</t>
-  </si>
-  <si>
-    <t>#39</t>
-  </si>
-  <si>
-    <t>#40</t>
-  </si>
-  <si>
-    <t>#41</t>
-  </si>
-  <si>
-    <t>#42</t>
-  </si>
-  <si>
-    <t>#43</t>
-  </si>
-  <si>
-    <t>#44</t>
-  </si>
-  <si>
-    <t>#45</t>
-  </si>
-  <si>
-    <t>#46</t>
-  </si>
-  <si>
-    <t>#47</t>
-  </si>
-  <si>
-    <t>#48</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>LC002_01</t>
-  </si>
-  <si>
-    <t>LC002_02</t>
-  </si>
-  <si>
-    <t>LC002_03</t>
-  </si>
-  <si>
-    <t>LC002_05</t>
-  </si>
-  <si>
-    <t>LC002_06</t>
-  </si>
-  <si>
-    <t>LC002_07</t>
-  </si>
-  <si>
-    <t>LC002_08</t>
-  </si>
-  <si>
-    <t>CO-BFF_01</t>
-  </si>
-  <si>
-    <t>CO-BFF_02</t>
-  </si>
-  <si>
-    <t>CO-BFF_03</t>
-  </si>
-  <si>
-    <t>CO-BFF_04</t>
-  </si>
-  <si>
-    <t>CO-BFF_05</t>
-  </si>
-  <si>
-    <t>CO-BFF_06</t>
-  </si>
-  <si>
-    <t>GDSA_DORADO</t>
-  </si>
-  <si>
-    <t>GDSA_NEGRO</t>
-  </si>
-  <si>
-    <t>GDSA_ROSA</t>
-  </si>
-  <si>
-    <t>DIY-KIT_02</t>
-  </si>
-  <si>
-    <t>DIY-KIT_04</t>
-  </si>
-  <si>
-    <t>DIY-KIT_08</t>
-  </si>
-  <si>
-    <t>DIY-KIT_10</t>
-  </si>
-  <si>
-    <t>DIY-KIT_12</t>
-  </si>
-  <si>
-    <t>DIY-KIT_13</t>
-  </si>
-  <si>
-    <t>DIY-KITSM_02</t>
-  </si>
-  <si>
-    <t>DIY-KITSM_04</t>
-  </si>
-  <si>
-    <t>DIY-KITSM_08</t>
-  </si>
-  <si>
-    <t>DIY-KITSM_10</t>
-  </si>
-  <si>
-    <t>DIY-KITSM_12</t>
-  </si>
-  <si>
-    <t>DIY-KITSM_133</t>
-  </si>
-  <si>
-    <t>3D-01_01</t>
-  </si>
-  <si>
-    <t>3D-01_02</t>
-  </si>
-  <si>
-    <t>3D-01_03</t>
-  </si>
-  <si>
-    <t>3D-01_04</t>
-  </si>
-  <si>
-    <t>3D-01_05</t>
-  </si>
-  <si>
-    <t>3D-01_06</t>
-  </si>
-  <si>
-    <t>3D-01_07</t>
-  </si>
-  <si>
-    <t>3D-01_08</t>
-  </si>
-  <si>
-    <t>3D-01_09</t>
-  </si>
-  <si>
-    <t>3D-01_10</t>
-  </si>
-  <si>
-    <t>3D-01_11</t>
-  </si>
-  <si>
-    <t>3D-01_12</t>
-  </si>
-  <si>
-    <t>3D-01_13</t>
-  </si>
-  <si>
-    <t>3D-01_14</t>
-  </si>
-  <si>
-    <t>3D-01_15</t>
-  </si>
-  <si>
-    <t>3D-01_16</t>
-  </si>
-  <si>
-    <t>3D-01_17</t>
-  </si>
-  <si>
-    <t>3D-01_18</t>
-  </si>
-  <si>
-    <t>3D-01_19</t>
-  </si>
-  <si>
-    <t>3D-01_20</t>
-  </si>
-  <si>
-    <t>3D-01_21</t>
-  </si>
-  <si>
-    <t>3D-01_22</t>
-  </si>
-  <si>
-    <t>3D-01_23</t>
-  </si>
-  <si>
-    <t>3D-01_24</t>
-  </si>
-  <si>
-    <t>3D-01_25</t>
-  </si>
-  <si>
-    <t>3D-01_26</t>
-  </si>
-  <si>
-    <t>3D-01_27</t>
-  </si>
-  <si>
-    <t>3D-01_28</t>
-  </si>
-  <si>
-    <t>3D-01_29</t>
-  </si>
-  <si>
-    <t>3D-01_30</t>
-  </si>
-  <si>
-    <t>3D-01_31</t>
-  </si>
-  <si>
-    <t>3D-01_32</t>
-  </si>
-  <si>
-    <t>3D-01_33</t>
-  </si>
-  <si>
-    <t>3D-01_34</t>
-  </si>
-  <si>
-    <t>3D-01_35</t>
-  </si>
-  <si>
-    <t>3D-01_36</t>
-  </si>
-  <si>
-    <t>3D-01_37</t>
-  </si>
-  <si>
-    <t>3D-01_38</t>
-  </si>
-  <si>
-    <t>3D-01_39</t>
-  </si>
-  <si>
-    <t>3D-01_40</t>
-  </si>
-  <si>
-    <t>3D-01_41</t>
-  </si>
-  <si>
-    <t>3D-01_42</t>
-  </si>
-  <si>
-    <t>3D-01_43</t>
-  </si>
-  <si>
-    <t>3D-01_44</t>
-  </si>
-  <si>
-    <t>3D-01_45</t>
-  </si>
-  <si>
-    <t>3D-01_46</t>
-  </si>
-  <si>
-    <t>3D-01_47</t>
-  </si>
-  <si>
-    <t>3D-01_48</t>
-  </si>
-  <si>
-    <t>DIY-ML_01</t>
-  </si>
-  <si>
-    <t>DIY-ML_02</t>
-  </si>
-  <si>
-    <t>DIY-ML_03</t>
-  </si>
-  <si>
-    <t>DIY-ML_04</t>
-  </si>
-  <si>
-    <t>DIY-ML_05</t>
-  </si>
-  <si>
-    <t>DIY-ML_06</t>
-  </si>
-  <si>
-    <t>DIY-ML_07</t>
-  </si>
-  <si>
-    <t>DIY-ML_08</t>
-  </si>
-  <si>
-    <t>DIY-ML_09</t>
-  </si>
-  <si>
-    <t>DIY-ML_10</t>
-  </si>
-  <si>
-    <t>DIY-ML_11</t>
-  </si>
-  <si>
-    <t>DIY-ML_12</t>
-  </si>
-  <si>
-    <t>DIY-ML_13</t>
-  </si>
-  <si>
-    <t>DIY-SM_01</t>
-  </si>
-  <si>
-    <t>DIY-SM_02</t>
-  </si>
-  <si>
-    <t>DIY-SM_03</t>
-  </si>
-  <si>
-    <t>DIY-SM_04</t>
-  </si>
-  <si>
-    <t>DIY-SM_05</t>
-  </si>
-  <si>
-    <t>DIY-SM_06</t>
-  </si>
-  <si>
-    <t>DIY-SM_07</t>
-  </si>
-  <si>
-    <t>DIY-SM_08</t>
-  </si>
-  <si>
-    <t>DIY-SM_09</t>
-  </si>
-  <si>
-    <t>DIY-SM_10</t>
-  </si>
-  <si>
-    <t>DIY-SM_11</t>
-  </si>
-  <si>
-    <t>DIY-SM_12</t>
-  </si>
-  <si>
-    <t>DIY-SM_13</t>
-  </si>
-  <si>
-    <t>EB001_01</t>
-  </si>
-  <si>
-    <t>EB001_02</t>
-  </si>
-  <si>
-    <t>EB001_03</t>
   </si>
 </sst>
 </file>
@@ -872,9 +872,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1293,22 +1293,22 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" s="1">
         <v>54.9</v>
@@ -1325,22 +1325,22 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" s="1">
         <v>47</v>
@@ -1357,22 +1357,22 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="1">
         <v>56</v>
@@ -1389,22 +1389,22 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1">
         <v>73.5</v>
@@ -1413,7 +1413,7 @@
         <v>5</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>18</v>
@@ -1421,22 +1421,22 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
         <v>73.5</v>
@@ -1453,22 +1453,22 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
         <v>73.5</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" s="1">
         <v>73.5</v>
@@ -1517,22 +1517,22 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" s="1">
         <v>73.5</v>
@@ -1549,22 +1549,22 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1">
         <v>73.5</v>
@@ -1581,22 +1581,22 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G13" s="1">
         <v>73.5</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" s="1">
         <v>73.5</v>
@@ -1645,22 +1645,22 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G15" s="1">
         <v>114</v>
@@ -1669,7 +1669,7 @@
         <v>5</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>18</v>
@@ -1677,22 +1677,22 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G16" s="1">
         <v>114</v>
@@ -1709,22 +1709,22 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="D17" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G17" s="1">
         <v>114</v>
@@ -1741,22 +1741,22 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G18" s="1">
         <v>114</v>
@@ -1773,22 +1773,22 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="D19" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G19" s="1">
         <v>114</v>
@@ -1805,22 +1805,22 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="D20" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G20" s="1">
         <v>114</v>
@@ -1837,22 +1837,22 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G21" s="1">
         <v>114</v>
@@ -1869,22 +1869,22 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G22" s="1">
         <v>72</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G23" s="1">
         <v>104.6</v>
@@ -1933,22 +1933,22 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G24" s="1">
         <v>104</v>
@@ -1965,22 +1965,22 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G25" s="1">
         <v>97</v>
@@ -1997,22 +1997,22 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G26" s="1">
         <v>78</v>
@@ -2021,7 +2021,7 @@
         <v>5</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>18</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G27" s="1">
         <v>78</v>
@@ -2061,22 +2061,22 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="D28" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G28" s="1">
         <v>78</v>
@@ -2093,22 +2093,22 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="D29" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G29" s="1">
         <v>78</v>
@@ -2125,22 +2125,22 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G30" s="1">
         <v>280.8</v>
@@ -2149,7 +2149,7 @@
         <v>5</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>18</v>
@@ -2157,22 +2157,22 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="D31" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G31" s="1">
         <v>280.8</v>
@@ -2189,22 +2189,22 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="D32" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G32" s="1">
         <v>280.8</v>
@@ -2221,22 +2221,22 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="D33" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G33" s="1">
         <v>280.8</v>
@@ -2253,22 +2253,22 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="D34" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G34" s="1">
         <v>280.8</v>
@@ -2285,22 +2285,22 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="D35" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G35" s="1">
         <v>280.8</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="D36" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G36" s="1">
         <v>280.8</v>
@@ -2349,22 +2349,22 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G37" s="1">
         <v>344</v>
@@ -2373,7 +2373,7 @@
         <v>5</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>18</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G38" s="1">
         <v>344</v>
@@ -2413,22 +2413,22 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G39" s="1">
         <v>344</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G40" s="1">
         <v>344</v>
@@ -2477,22 +2477,22 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G41" s="1">
         <v>344</v>
@@ -2509,22 +2509,22 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G42" s="1">
         <v>344</v>
@@ -2541,22 +2541,22 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G43" s="1">
         <v>344</v>
@@ -2573,22 +2573,22 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G44" s="1">
         <v>54</v>
@@ -2605,22 +2605,22 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G45" s="1">
         <v>102</v>
@@ -2637,22 +2637,22 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G46" s="1">
         <v>163</v>
@@ -2669,22 +2669,22 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G47" s="1">
         <v>40.5</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>18</v>
@@ -2701,22 +2701,22 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G48" s="1">
         <v>40.5</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G49" s="1">
         <v>40.5</v>
@@ -2765,22 +2765,22 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G50" s="1">
         <v>40.5</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G51" s="1">
         <v>40.5</v>
@@ -2829,22 +2829,22 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G52" s="1">
         <v>40.5</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G53" s="1">
         <v>40.5</v>
@@ -2893,22 +2893,22 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G54" s="1">
         <v>40.5</v>
@@ -2925,22 +2925,22 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G55" s="1">
         <v>40.5</v>
@@ -2957,22 +2957,22 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G56" s="1">
         <v>40.5</v>
@@ -2989,22 +2989,22 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G57" s="1">
         <v>40.5</v>
@@ -3021,22 +3021,22 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G58" s="1">
         <v>40.5</v>
@@ -3053,22 +3053,22 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G59" s="1">
         <v>40.5</v>
@@ -3085,22 +3085,22 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G60" s="1">
         <v>40.5</v>
@@ -3117,22 +3117,22 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G61" s="1">
         <v>40.5</v>
@@ -3149,22 +3149,22 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G62" s="1">
         <v>40.5</v>
@@ -3181,22 +3181,22 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G63" s="1">
         <v>40.5</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G64" s="1">
         <v>40.5</v>
@@ -3245,22 +3245,22 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G65" s="1">
         <v>40.5</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G66" s="1">
         <v>40.5</v>
@@ -3309,22 +3309,22 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G67" s="1">
         <v>40.5</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G68" s="1">
         <v>40.5</v>
@@ -3373,22 +3373,22 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G69" s="1">
         <v>40.5</v>
@@ -3405,22 +3405,22 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G70" s="1">
         <v>40.5</v>
@@ -3437,22 +3437,22 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G71" s="1">
         <v>40.5</v>
@@ -3469,22 +3469,22 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G72" s="1">
         <v>40.5</v>
@@ -3501,22 +3501,22 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G73" s="1">
         <v>40.5</v>
@@ -3533,22 +3533,22 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G74" s="1">
         <v>40.5</v>
@@ -3565,22 +3565,22 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G75" s="1">
         <v>40.5</v>
@@ -3597,22 +3597,22 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G76" s="1">
         <v>40.5</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G77" s="1">
         <v>40.5</v>
@@ -3661,22 +3661,22 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G78" s="1">
         <v>40.5</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G79" s="1">
         <v>40.5</v>
@@ -3725,22 +3725,22 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G80" s="1">
         <v>40.5</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G81" s="1">
         <v>40.5</v>
@@ -3789,22 +3789,22 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G82" s="1">
         <v>40.5</v>
@@ -3821,22 +3821,22 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G83" s="1">
         <v>40.5</v>
@@ -3853,22 +3853,22 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G84" s="1">
         <v>40.5</v>
@@ -3885,22 +3885,22 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G85" s="1">
         <v>40.5</v>
@@ -3917,22 +3917,22 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G86" s="1">
         <v>40.5</v>
@@ -3949,22 +3949,22 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G87" s="1">
         <v>40.5</v>
@@ -3981,22 +3981,22 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G88" s="1">
         <v>40.5</v>
@@ -4013,22 +4013,22 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G89" s="1">
         <v>40.5</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G90" s="1">
         <v>40.5</v>
@@ -4077,22 +4077,22 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G91" s="1">
         <v>40.5</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G92" s="1">
         <v>40.5</v>
@@ -4141,22 +4141,22 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G93" s="1">
         <v>40.5</v>
@@ -4173,22 +4173,22 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G94" s="1">
         <v>40.5</v>
@@ -4205,22 +4205,22 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G95" s="1">
         <v>40.5</v>
@@ -4237,22 +4237,22 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G96" s="1">
         <v>183.3</v>
@@ -4261,7 +4261,7 @@
         <v>5</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>18</v>
@@ -4269,22 +4269,22 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G97" s="1">
         <v>183.3</v>
@@ -4301,22 +4301,22 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G98" s="1">
         <v>183.3</v>
@@ -4333,22 +4333,22 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G99" s="1">
         <v>183.3</v>
@@ -4365,22 +4365,22 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G100" s="1">
         <v>183.3</v>
@@ -4397,22 +4397,22 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G101" s="1">
         <v>183.3</v>
@@ -4429,22 +4429,22 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G102" s="1">
         <v>183.3</v>
@@ -4461,22 +4461,22 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G103" s="1">
         <v>183.3</v>
@@ -4493,22 +4493,22 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G104" s="1">
         <v>183.3</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G105" s="1">
         <v>183.3</v>
@@ -4557,22 +4557,22 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G106" s="1">
         <v>183.3</v>
@@ -4589,22 +4589,22 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G107" s="1">
         <v>183.3</v>
@@ -4621,22 +4621,22 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G108" s="1">
         <v>183.3</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G109" s="1">
         <v>183.3</v>
@@ -4685,22 +4685,22 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G110" s="1">
         <v>183.3</v>
@@ -4709,7 +4709,7 @@
         <v>5</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="J110" s="1" t="s">
         <v>18</v>
@@ -4717,22 +4717,22 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G111" s="1">
         <v>183.3</v>
@@ -4749,22 +4749,22 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G112" s="1">
         <v>183.3</v>
@@ -4781,22 +4781,22 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G113" s="1">
         <v>183.3</v>
@@ -4813,22 +4813,22 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G114" s="1">
         <v>183.3</v>
@@ -4845,22 +4845,22 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G115" s="1">
         <v>183.3</v>
@@ -4877,22 +4877,22 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G116" s="1">
         <v>183.3</v>
@@ -4909,22 +4909,22 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G117" s="1">
         <v>183.3</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G118" s="1">
         <v>183.3</v>
@@ -4973,22 +4973,22 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G119" s="1">
         <v>183.3</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G120" s="1">
         <v>183.3</v>
@@ -5037,22 +5037,22 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G121" s="1">
         <v>183.3</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G122" s="1">
         <v>183.3</v>
@@ -5101,22 +5101,22 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G123" s="1">
         <v>183.3</v>
@@ -5133,22 +5133,22 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G124" s="1">
         <v>78</v>
@@ -5165,22 +5165,22 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B125" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G125" s="1">
         <v>57</v>
@@ -5197,22 +5197,22 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B126" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G126" s="1">
         <v>57.8</v>
@@ -5221,7 +5221,7 @@
         <v>5</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="J126" s="1" t="s">
         <v>18</v>
@@ -5229,22 +5229,22 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B127" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="D127" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G127" s="1">
         <v>57.8</v>
@@ -5261,22 +5261,22 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B128" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="D128" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G128" s="1">
         <v>57.8</v>
@@ -5293,22 +5293,22 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="D129" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G129" s="1">
         <v>57.8</v>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charlyboyapple/bellezagdl-backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAA95BE-2A93-9C4C-9764-7BAA535FAA66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD91EBE6-629D-874C-8346-4DDDC1498EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15700" yWindow="4800" windowWidth="31240" windowHeight="13460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29360" yWindow="5500" windowWidth="31240" windowHeight="13460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="260">
   <si>
     <t>Alby</t>
   </si>
@@ -807,6 +807,12 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>oferta</t>
+  </si>
+  <si>
+    <t>precio_oferta</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="37.33203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" style="1" customWidth="1"/>
@@ -1192,10 +1198,12 @@
     <col min="8" max="8" width="16.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="37.33203125" style="1"/>
+    <col min="11" max="11" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="37.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -1226,8 +1234,14 @@
       <c r="J1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1258,8 +1272,14 @@
       <c r="J2" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1290,8 +1310,14 @@
       <c r="J3" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -1322,8 +1348,14 @@
       <c r="J4" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="1">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -1355,7 +1387,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,7 +1419,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1418,8 +1450,14 @@
       <c r="J7" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -1451,7 +1489,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -1483,7 +1521,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1515,7 +1553,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1547,7 +1585,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1579,7 +1617,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1611,7 +1649,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -1643,7 +1681,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -1674,8 +1712,14 @@
       <c r="J15" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="1">
+        <v>99.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
